--- a/Result/profitability/4127.xlsx
+++ b/Result/profitability/4127.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09499999999999989</v>
+        <v>0.1249999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>59.52999999999999</v>
+        <v>59.4175</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.16</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1062499999999999</v>
+        <v>0.1324999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>60.48125</v>
+        <v>60.985</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.16</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1137499999999999</v>
+        <v>0.1037499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>62.29875</v>
+        <v>62.46875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,16 +1018,16 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05624999999999989</v>
+        <v>0.2274999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>61.92</v>
+        <v>62.63250000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.34</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2312499999999999</v>
+        <v>0.2062499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>62.87875</v>
+        <v>63.595</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1712499999999999</v>
+        <v>0.2174999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>63.19</v>
+        <v>63.7075</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.17</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1999999999999999</v>
+        <v>0.1449999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>63.8825</v>
+        <v>63.9875</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-0.08</v>
       </c>
       <c r="M9" t="n">
-        <v>0.09624999999999991</v>
+        <v>0.09624999999999989</v>
       </c>
       <c r="N9" t="n">
         <v>64.33875</v>
@@ -1648,7 +1648,7 @@
         <v>0.1949999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>63.63250000000001</v>
+        <v>63.63249999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4127</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>185</v>
+      </c>
+      <c r="D75" t="n">
+        <v>73</v>
+      </c>
+      <c r="E75" t="n">
+        <v>112</v>
+      </c>
+      <c r="F75" t="n">
+        <v>60.58</v>
+      </c>
+      <c r="G75" t="n">
+        <v>10</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.31%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>13</v>
+      </c>
+      <c r="K75" t="n">
+        <v>14</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1262499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>57.96749999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5866666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.8399999999999963</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.0140609306996986</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.292452830188679</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.699999999999996</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1038629737609329</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
